--- a/artfynd/A 28145-2025 artfynd.xlsx
+++ b/artfynd/A 28145-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,616 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126428905</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>593671</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6972692</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126429323</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>593603</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6972663</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126429470</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593595</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6972640</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126429373</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593603</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6972663</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126429275</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>593603</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6972663</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126428975</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57816</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593674</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6972679</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28145-2025 artfynd.xlsx
+++ b/artfynd/A 28145-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126428905</v>
       </c>
       <c r="B3" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126429323</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126429470</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126429373</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126429275</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>126428975</v>
       </c>
       <c r="B8" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28145-2025 artfynd.xlsx
+++ b/artfynd/A 28145-2025 artfynd.xlsx
@@ -1172,7 +1172,7 @@
         <v>126429275</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28145-2025 artfynd.xlsx
+++ b/artfynd/A 28145-2025 artfynd.xlsx
@@ -1172,7 +1172,7 @@
         <v>126429275</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28145-2025 artfynd.xlsx
+++ b/artfynd/A 28145-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112610669</v>
       </c>
       <c r="B2" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593666</v>
+        <v>593667</v>
       </c>
       <c r="R2" t="n">
         <v>6972614</v>
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126428905</v>
+        <v>126429348</v>
       </c>
       <c r="B3" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593671</v>
+        <v>593583</v>
       </c>
       <c r="R3" t="n">
-        <v>6972692</v>
+        <v>6972669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,39 +869,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126429323</v>
+        <v>126429373</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fisklössjöflon, Mpd</t>
@@ -978,11 +969,11 @@
         <v>126429470</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1072,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126429373</v>
+        <v>126428905</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593603</v>
+        <v>593671</v>
       </c>
       <c r="R6" t="n">
-        <v>6972663</v>
+        <v>6972692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126429275</v>
+        <v>126429246</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1203,7 @@
         <v>593603</v>
       </c>
       <c r="R7" t="n">
-        <v>6972663</v>
+        <v>6972689</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126428975</v>
+        <v>126429275</v>
       </c>
       <c r="B8" t="n">
-        <v>57817</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,36 +1278,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1325,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593674</v>
+        <v>593603</v>
       </c>
       <c r="R8" t="n">
-        <v>6972679</v>
+        <v>6972663</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1345,11 @@
           <t>2025-07-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1384,6 +1371,218 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126428975</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>593674</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972679</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126429323</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593603</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6972663</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28145-2025 artfynd.xlsx
+++ b/artfynd/A 28145-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610669</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429470</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126428905</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429246</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429275</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126428975</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,8 +1628,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429323</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>